--- a/output/walk_forward_reports/walk_comparison.xlsx
+++ b/output/walk_forward_reports/walk_comparison.xlsx
@@ -1,26 +1,152 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\qqq\output\walk_forward_reports\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A362B81-C7C9-4C7B-8540-FC0BF123452C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="35">
+  <si>
+    <t>walk_id</t>
+  </si>
+  <si>
+    <t>train_start</t>
+  </si>
+  <si>
+    <t>train_end</t>
+  </si>
+  <si>
+    <t>test_start</t>
+  </si>
+  <si>
+    <t>test_end</t>
+  </si>
+  <si>
+    <t>best_strategy</t>
+  </si>
+  <si>
+    <t>best_sharpe</t>
+  </si>
+  <si>
+    <t>worst_strategy</t>
+  </si>
+  <si>
+    <t>worst_sharpe</t>
+  </si>
+  <si>
+    <t>avg_sharpe</t>
+  </si>
+  <si>
+    <t>median_sharpe</t>
+  </si>
+  <si>
+    <t>sharpe_range</t>
+  </si>
+  <si>
+    <t>positive_sharpe_ratio</t>
+  </si>
+  <si>
+    <t>factor_score_10G_Top3_P10d</t>
+  </si>
+  <si>
+    <t>mvo_5G_Top2_P10d</t>
+  </si>
+  <si>
+    <t>factor_score_5G_Top2_P20d</t>
+  </si>
+  <si>
+    <t>max_return_10G_Top1_P30d</t>
+  </si>
+  <si>
+    <t>mvo_10G_Top3_P30d</t>
+  </si>
+  <si>
+    <t>max_return_5G_Top3_P30d</t>
+  </si>
+  <si>
+    <t>equal_5G_Top3_P60d</t>
+  </si>
+  <si>
+    <t>mvo_10G_Top2_P20d</t>
+  </si>
+  <si>
+    <t>mvo_5G_Top1_P20d</t>
+  </si>
+  <si>
+    <t>equal_10G_Top3_P60d</t>
+  </si>
+  <si>
+    <t>factor_score_10G_Top2_P60d</t>
+  </si>
+  <si>
+    <t>max_return_10G_Top2_P20d</t>
+  </si>
+  <si>
+    <t>equal_10G_Top2_P60d</t>
+  </si>
+  <si>
+    <t>min_variance_10G_Top2_P30d</t>
+  </si>
+  <si>
+    <t>max_return_10G_Top1_P20d</t>
+  </si>
+  <si>
+    <t>max_return_5G_Top2_P20d</t>
+  </si>
+  <si>
+    <t>mvo_5G_Top3_P30d</t>
+  </si>
+  <si>
+    <t>factor_score_10G_Top2_P30d</t>
+  </si>
+  <si>
+    <t>max_return_5G_Top1_P30d</t>
+  </si>
+  <si>
+    <t>max_return_5G_Top3_P10d</t>
+  </si>
+  <si>
+    <t>equal_10G_Top2_P30d</t>
+  </si>
+  <si>
+    <t>max_return_5G_Top2_P30d</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -44,21 +170,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -96,7 +231,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -130,6 +265,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -164,9 +300,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -339,10 +476,558 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:M13"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="21.08984375" customWidth="1"/>
+    <col min="3" max="3" width="20.6328125" customWidth="1"/>
+    <col min="4" max="5" width="21.90625" customWidth="1"/>
+    <col min="6" max="6" width="22.08984375" customWidth="1"/>
+    <col min="7" max="7" width="20.36328125" customWidth="1"/>
+    <col min="8" max="8" width="16.08984375" customWidth="1"/>
+    <col min="9" max="9" width="17.1796875" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="15.1796875" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
+    <col min="13" max="13" width="12.36328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1">
+        <v>44929</v>
+      </c>
+      <c r="C2" s="1">
+        <v>45510</v>
+      </c>
+      <c r="D2" s="1">
+        <v>45511</v>
+      </c>
+      <c r="E2" s="1">
+        <v>45595</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2">
+        <v>8.1625586737548979</v>
+      </c>
+      <c r="H2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2">
+        <v>0.15521958534588801</v>
+      </c>
+      <c r="J2">
+        <v>3.708534471832484</v>
+      </c>
+      <c r="K2">
+        <v>3.7869787694943509</v>
+      </c>
+      <c r="L2">
+        <v>8.0073390884090099</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1">
+        <v>44972</v>
+      </c>
+      <c r="C3" s="1">
+        <v>45553</v>
+      </c>
+      <c r="D3" s="1">
+        <v>45554</v>
+      </c>
+      <c r="E3" s="1">
+        <v>45638</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3">
+        <v>3.919852877756306</v>
+      </c>
+      <c r="H3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3">
+        <v>-5.2880309089975546</v>
+      </c>
+      <c r="J3">
+        <v>0.6441817354822218</v>
+      </c>
+      <c r="K3">
+        <v>0.73227880390412925</v>
+      </c>
+      <c r="L3">
+        <v>9.207883786753861</v>
+      </c>
+      <c r="M3">
+        <v>0.73333333333333328</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1">
+        <v>45015</v>
+      </c>
+      <c r="C4" s="1">
+        <v>45595</v>
+      </c>
+      <c r="D4" s="1">
+        <v>45596</v>
+      </c>
+      <c r="E4" s="1">
+        <v>45686</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4">
+        <v>4.4803054259444384</v>
+      </c>
+      <c r="H4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4">
+        <v>-2.9378038063171181</v>
+      </c>
+      <c r="J4">
+        <v>0.47932891778164</v>
+      </c>
+      <c r="K4">
+        <v>0.69101708237783921</v>
+      </c>
+      <c r="L4">
+        <v>7.4181092322615569</v>
+      </c>
+      <c r="M4">
+        <v>0.71666666666666667</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1">
+        <v>45058</v>
+      </c>
+      <c r="C5" s="1">
+        <v>45638</v>
+      </c>
+      <c r="D5" s="1">
+        <v>45639</v>
+      </c>
+      <c r="E5" s="1">
+        <v>45729</v>
+      </c>
+      <c r="F5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5">
+        <v>3.3367281459700018</v>
+      </c>
+      <c r="H5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5">
+        <v>-5.6060601937105696</v>
+      </c>
+      <c r="J5">
+        <v>8.6697662150144086E-2</v>
+      </c>
+      <c r="K5">
+        <v>0.61073486220154449</v>
+      </c>
+      <c r="L5">
+        <v>8.9427883396805719</v>
+      </c>
+      <c r="M5">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1">
+        <v>45104</v>
+      </c>
+      <c r="C6" s="1">
+        <v>45686</v>
+      </c>
+      <c r="D6" s="1">
+        <v>45687</v>
+      </c>
+      <c r="E6" s="1">
+        <v>45772</v>
+      </c>
+      <c r="F6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6">
+        <v>1.048816932037365</v>
+      </c>
+      <c r="H6" t="s">
+        <v>28</v>
+      </c>
+      <c r="I6">
+        <v>-3.531678948258091</v>
+      </c>
+      <c r="J6">
+        <v>-1.2734290418146861</v>
+      </c>
+      <c r="K6">
+        <v>-1.31661338993704</v>
+      </c>
+      <c r="L6">
+        <v>4.5804958802954552</v>
+      </c>
+      <c r="M6">
+        <v>9.166666666666666E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1">
+        <v>45147</v>
+      </c>
+      <c r="C7" s="1">
+        <v>45729</v>
+      </c>
+      <c r="D7" s="1">
+        <v>45730</v>
+      </c>
+      <c r="E7" s="1">
+        <v>45817</v>
+      </c>
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7">
+        <v>2.0623047401629</v>
+      </c>
+      <c r="H7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I7">
+        <v>-3.9447806813881781</v>
+      </c>
+      <c r="J7">
+        <v>0.32643377703583459</v>
+      </c>
+      <c r="K7">
+        <v>0.40831464442996801</v>
+      </c>
+      <c r="L7">
+        <v>6.0070854215510776</v>
+      </c>
+      <c r="M7">
+        <v>0.71666666666666667</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1">
+        <v>45190</v>
+      </c>
+      <c r="C8" s="1">
+        <v>45772</v>
+      </c>
+      <c r="D8" s="1">
+        <v>45775</v>
+      </c>
+      <c r="E8" s="1">
+        <v>45861</v>
+      </c>
+      <c r="F8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8">
+        <v>6.4440104331307646</v>
+      </c>
+      <c r="H8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8">
+        <v>-9.6355915360685537E-2</v>
+      </c>
+      <c r="J8">
+        <v>3.1076114084099982</v>
+      </c>
+      <c r="K8">
+        <v>2.964828201801021</v>
+      </c>
+      <c r="L8">
+        <v>6.5403663484914514</v>
+      </c>
+      <c r="M8">
+        <v>0.98333333333333328</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1">
+        <v>45232</v>
+      </c>
+      <c r="C9" s="1">
+        <v>45817</v>
+      </c>
+      <c r="D9" s="1">
+        <v>45818</v>
+      </c>
+      <c r="E9" s="1">
+        <v>45904</v>
+      </c>
+      <c r="F9" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9">
+        <v>5.1828218941133368</v>
+      </c>
+      <c r="H9" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9">
+        <v>-3.8610608159959372</v>
+      </c>
+      <c r="J9">
+        <v>0.90179833564990919</v>
+      </c>
+      <c r="K9">
+        <v>0.88368697987891742</v>
+      </c>
+      <c r="L9">
+        <v>9.0438827101092727</v>
+      </c>
+      <c r="M9">
+        <v>0.70833333333333337</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1">
+        <v>45275</v>
+      </c>
+      <c r="C10" s="1">
+        <v>45861</v>
+      </c>
+      <c r="D10" s="1">
+        <v>45862</v>
+      </c>
+      <c r="E10" s="1">
+        <v>45946</v>
+      </c>
+      <c r="F10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10">
+        <v>4.1501831563250828</v>
+      </c>
+      <c r="H10" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10">
+        <v>-2.51696258256968</v>
+      </c>
+      <c r="J10">
+        <v>0.8572358746067773</v>
+      </c>
+      <c r="K10">
+        <v>0.85925975799366816</v>
+      </c>
+      <c r="L10">
+        <v>6.6671457388947619</v>
+      </c>
+      <c r="M10">
+        <v>0.73333333333333328</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" s="1">
+        <v>45322</v>
+      </c>
+      <c r="C11" s="1">
+        <v>45904</v>
+      </c>
+      <c r="D11" s="1">
+        <v>45905</v>
+      </c>
+      <c r="E11" s="1">
+        <v>45989</v>
+      </c>
+      <c r="F11" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11">
+        <v>3.8680649805194571</v>
+      </c>
+      <c r="H11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I11">
+        <v>-1.8994425426496919</v>
+      </c>
+      <c r="J11">
+        <v>1.21046427689054</v>
+      </c>
+      <c r="K11">
+        <v>1.4615168529398279</v>
+      </c>
+      <c r="L11">
+        <v>5.7675075231691491</v>
+      </c>
+      <c r="M11">
+        <v>0.77500000000000002</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" s="1">
+        <v>45365</v>
+      </c>
+      <c r="C12" s="1">
+        <v>45946</v>
+      </c>
+      <c r="D12" s="1">
+        <v>45947</v>
+      </c>
+      <c r="E12" s="1">
+        <v>46035</v>
+      </c>
+      <c r="F12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12">
+        <v>4.7021958533770922</v>
+      </c>
+      <c r="H12" t="s">
+        <v>33</v>
+      </c>
+      <c r="I12">
+        <v>-3.0600362443652811</v>
+      </c>
+      <c r="J12">
+        <v>0.72278586060174155</v>
+      </c>
+      <c r="K12">
+        <v>0.79014316522591321</v>
+      </c>
+      <c r="L12">
+        <v>7.7622320977423733</v>
+      </c>
+      <c r="M12">
+        <v>0.72499999999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" s="1">
+        <v>45408</v>
+      </c>
+      <c r="C13" s="1">
+        <v>45989</v>
+      </c>
+      <c r="D13" s="1">
+        <v>45992</v>
+      </c>
+      <c r="E13" s="1">
+        <v>46079</v>
+      </c>
+      <c r="F13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13">
+        <v>5.2930734443818386</v>
+      </c>
+      <c r="H13" t="s">
+        <v>34</v>
+      </c>
+      <c r="I13">
+        <v>-1.7962151708272029</v>
+      </c>
+      <c r="J13">
+        <v>2.0745989565481748</v>
+      </c>
+      <c r="K13">
+        <v>2.0518971648311801</v>
+      </c>
+      <c r="L13">
+        <v>7.0892886152090417</v>
+      </c>
+      <c r="M13">
+        <v>0.89166666666666672</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>